--- a/mixs-templates/Misag_plus_combinations/MisagFoodFarmEnvironment.xlsx
+++ b/mixs-templates/Misag_plus_combinations/MisagFoodFarmEnvironment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GI1"/>
+  <dimension ref="A1:GK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,760 +614,770 @@
       </c>
       <c r="AN1" t="inlineStr">
         <is>
+          <t>marker_gene_recov</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>marker_gene_recov_sw</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
           <t>pos_cont_type</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>feat_pred</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>compl_software</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>env_local_scale</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>sort_tech</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>samp_mat_process</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>sim_search_meth</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>samp_collect_method</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>wga_amp_appr</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>compl_appr</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>env_medium</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>samp_taxon_id</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>geo_loc_name</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>sc_lysis_approach</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>collection_date</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>seq_meth</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>lat_lon</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>elev</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>env_broad_scale</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>tax_class</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>experimental_factor</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>associated_resource</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>sop</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>humidity</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>organism_count</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>spikein_count</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>samp_store_temp</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>solar_irradiance</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>ventilation_rate</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>samp_store_dur</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>wind_speed</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>salinity</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>previous_land_use</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>crop_rotation</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>soil_type_meth</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>tot_org_c_meth</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>tot_nitro_cont_meth</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>host_age</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>host_dry_mass</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>host_height</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>host_length</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>host_tot_mass</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>root_med_carbon</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>root_med_macronutr</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>root_med_micronutr</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>season_temp</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>season_precpt</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>tot_org_carb</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>tot_nitro_content</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>conduc</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>turbidity</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>size_frac_low</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>size_frac_up</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>ventilation_type</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>wind_direction</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>genetic_mod</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>host_phenotype</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>ph</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>ances_data</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>biotic_regm</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>chem_administration</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>growth_habit</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>host_disease_stat</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>host_genotype</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>host_taxid</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>mechanical_damage</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>perturbation</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>root_cond</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>root_med_ph</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>tillage</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>ph_meth</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>growth_medium</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>food_product_type</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>samp_type</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>farm_water_source</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>plant_water_method</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>air_PM_concen</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>animal_feed_equip</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>animal_intrusion</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>anim_water_method</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>crop_yield</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>cult_result</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>cult_result_org</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>cult_target</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>plant_part_maturity</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>adjacent_environment</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>water_source_adjac</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>farm_equip_shared</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>farm_equip_san</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>farm_equip_san_freq</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>farm_equip</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fertilizer_admin</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fertilizer_date</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>animal_group_size</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>animal_diet</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>food_contact_surf</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>food_contain_wrap</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>food_harvest_proc</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>food_pack_medium</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>food_preserv_proc</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>food_prod_char</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>prod_label_claims</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>food_trav_mode</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>food_trav_vehic</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>food_source</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>food_treat_proc</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>extr_weather_event</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>date_extr_weath</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>host_subspecf_genlin</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>intended_consumer</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>library_prep_kit</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>air_flow_impede</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>lot_number</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>season_humidity</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>part_plant_animal</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>plant_growth_med</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>plant_reprod_crop</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>samp_purpose</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>repository_name</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>samp_pooling</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>samp_source_mat_cat</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>sequencing_kit</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>sequencing_location</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>serovar_or_serotype</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>soil_conductivity</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>soil_cover</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>soil_pH</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>rel_location</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>soil_porosity</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>soil_temp</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>soil_texture_class</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>soil_texture_meth</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>soil_type</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>spikein_org</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>spikein_serovar</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>spikein_growth_med</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>spikein_strain</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>spikein_antibiotic</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>spikein_metal</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>timepoint</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>water_frequency</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>water_pH</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>water_source_shared</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>enrichment_protocol</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>food_quality_date</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>IFSAC_category</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>animal_housing</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>cult_isol_date</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>food_clean_proc</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>misc_param</t>
         </is>
@@ -1393,43 +1403,43 @@
     <dataValidation sqref="AI2:AI1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"16S rRNA gene,multi-marker approach,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AT2:AT1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"flow cytometric cell sorting,lazer-tweezing,microfluidics,micromanipulation,optical manipulation,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AW2:AW1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AY2:AY1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"mda based,pcr based"</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AZ2:AZ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"marker gene,other,reference based"</formula1>
     </dataValidation>
-    <dataValidation sqref="BB2:BB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BD2:BD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"chemical,combination,enzymatic,physical"</formula1>
     </dataValidation>
-    <dataValidation sqref="CX2:CX1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CZ2:CZ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"erect,prostrate,semi-erect,spreading"</formula1>
     </dataValidation>
-    <dataValidation sqref="DF2:DF1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="DH2:DH1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"chisel,cutting disc,disc plough,drill,mouldboard,ridge till,strip tillage,tined,zonal tillage"</formula1>
     </dataValidation>
-    <dataValidation sqref="DI2:DI1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="DK2:DK1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"autumn [NCIT:C94733],spring [NCIT:C94731],summer [NCIT:C94732],winter [NCIT:C94730]"</formula1>
     </dataValidation>
-    <dataValidation sqref="DL2:DL1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="DN2:DN1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"brackish,canal,collected rainwater,ditch,estuary,freshwater,lake,manmade,melt pond,municipal,natural,pond,reservior,river,saline,storage tank,stream,well"</formula1>
     </dataValidation>
-    <dataValidation sqref="DS2:DS1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="DU2:DU1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"absent,active,inactive,negative,no,positive,present,yes"</formula1>
     </dataValidation>
-    <dataValidation sqref="ER2:ER1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="ET2:ET1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"drought,dust storm,extreme cold,extreme heat,flood,frost,hail,high precipitation,high winds"</formula1>
     </dataValidation>
-    <dataValidation sqref="FB2:FB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="FD2:FD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"plant cutting,pregerminated seed,ratoon,seed,seedling,whole mature plant"</formula1>
     </dataValidation>
-    <dataValidation sqref="FP2:FP1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="FR2:FR1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"clay,clay loam,loam,loamy sand,sand,sandy clay,sandy clay loam,sandy loam,silt,silt loam,silty clay,silty clay loam"</formula1>
     </dataValidation>
-    <dataValidation sqref="GH2:GH1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="GJ2:GJ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"drum and drain,manual spinner,rinsed with sanitizer solution,rinsed with water,scrubbed with brush,scrubbed with hand,soaking"</formula1>
     </dataValidation>
   </dataValidations>
